--- a/exports/BCA-A_Full_Report_April_2026.xlsx
+++ b/exports/BCA-A_Full_Report_April_2026.xlsx
@@ -27,14 +27,27 @@
     </font>
     <font>
       <b val="1"/>
+      <color rgb="00FFFFFF"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="001A3A6B"/>
+        <bgColor rgb="001A3A6B"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F2DCDB"/>
+        <bgColor rgb="00F2DCDB"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -49,9 +62,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -417,8 +435,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B7"/>
+  <dimension ref="A1:E7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="17" customWidth="1" min="3" max="3"/>
+    <col width="19" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
@@ -431,6 +456,21 @@
           <t>Name</t>
         </is>
       </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Total Classes</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Classes Present</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Attendance %</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -443,6 +483,15 @@
           <t>Anshika Bharti</t>
         </is>
       </c>
+      <c r="C2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -455,6 +504,15 @@
           <t>Rohan Verma</t>
         </is>
       </c>
+      <c r="C3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E3" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -467,6 +525,15 @@
           <t>Priya Kapoor</t>
         </is>
       </c>
+      <c r="C4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E4" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -479,6 +546,15 @@
           <t>Drishti paras</t>
         </is>
       </c>
+      <c r="C5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -491,6 +567,15 @@
           <t>Ishan sharma</t>
         </is>
       </c>
+      <c r="C6" t="n">
+        <v>0</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -502,6 +587,15 @@
         <is>
           <t>Rohit Kumar</t>
         </is>
+      </c>
+      <c r="C7" t="n">
+        <v>0</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" s="2" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
